--- a/04_DESIGN_TABLES/DesignTable_6400.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6400.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookups" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Lookups" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE67"/>
+  <dimension ref="A1:AF67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -644,6 +644,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -752,12 +757,17 @@
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p014-t02: agrees on D1@DRIVE, HEXB@HEX, D3@BORE_B, D4@BORE_A</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>6400-02-02-O</t>
         </is>
       </c>
     </row>
@@ -858,7 +868,7 @@
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
@@ -866,7 +876,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr"/>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.1~1.10; HEXB@HEX=0.5~0.500; D3@BORE_B=0.13~0.125; D4@BORE_A=0.13~0.125</t>
+        </is>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -975,7 +989,7 @@
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
@@ -983,7 +997,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.17~1.17; HEXB@HEX=0.5~0.500; D3@BORE_B=0.17~0.172; D4@BORE_A=0.06~0.062</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1092,7 +1110,7 @@
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
@@ -1100,7 +1118,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.17~1.17; HEXB@HEX=0.5~0.500; D3@BORE_B=0.17~0.172; D4@BORE_A=0.13~0.125</t>
+        </is>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1326,7 +1348,7 @@
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
@@ -1334,7 +1356,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC8" s="3" t="inlineStr"/>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.23~1.23; HEXB@HEX=0.625~0.625; D3@BORE_B=0.17~0.172; D4@BORE_A=0.23~0.234</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1443,7 +1469,7 @@
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
@@ -1451,7 +1477,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC9" s="3" t="inlineStr"/>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.29~1.29; HEXB@HEX=0.6875~0.688; D3@BORE_B=0.17~0.172; D4@BORE_A=0.3~0.297</t>
+        </is>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1560,7 +1590,7 @@
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
@@ -1568,7 +1598,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.37~1.37; HEXB@HEX=0.875~0.875; D3@BORE_B=0.17~0.172; D4@BORE_A=0.39~0.391</t>
+        </is>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1677,7 +1711,7 @@
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
@@ -1685,7 +1719,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.49~1.49; HEXB@HEX=1~1.000; D3@BORE_B=0.17~0.172; D4@BORE_A=0.48~0.484</t>
+        </is>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1794,7 +1832,7 @@
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
@@ -1802,7 +1840,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC12" s="3" t="inlineStr"/>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.66~1.66; HEXB@HEX=1.25~1.250; D3@BORE_B=0.17~0.172; D4@BORE_A=0.61~0.609</t>
+        </is>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1911,7 +1953,7 @@
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
@@ -1919,7 +1961,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.23~1.23; HEXB@HEX=0.5625~0.562; D3@BORE_B=0.23~0.234; D4@BORE_A=0.17~0.172</t>
+        </is>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2028,7 +2074,7 @@
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
@@ -2036,7 +2082,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.23~1.23; HEXB@HEX=0.625~0.625; D3@BORE_B=0.23~0.234; D4@BORE_A=0.23~0.234</t>
+        </is>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2145,7 +2195,7 @@
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
@@ -2153,7 +2203,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.29~1.29; HEXB@HEX=0.6875~0.688; D3@BORE_B=0.23~0.234; D4@BORE_A=0.3~0.297</t>
+        </is>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2378,7 +2432,7 @@
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
@@ -2386,7 +2440,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC17" s="3" t="inlineStr"/>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.27~1.27; HEXB@HEX=0.625~0.625; D3@BORE_B=0.3~0.297; D4@BORE_A=0.17~0.172</t>
+        </is>
+      </c>
       <c r="AD17" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2495,7 +2553,7 @@
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
@@ -2503,7 +2561,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC18" s="3" t="inlineStr"/>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.27~1.27; HEXB@HEX=0.625~0.625; D3@BORE_B=0.3~0.297; D4@BORE_A=0.23~0.234</t>
+        </is>
+      </c>
       <c r="AD18" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2687,7 +2749,7 @@
         <v>0.3</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.3</v>
+        <v>0.391</v>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
@@ -2734,10 +2796,14 @@
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
-        </is>
-      </c>
-      <c r="AC20" s="3" t="inlineStr"/>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); D4@BORE_A: OMi WebsitePartsInfo2026.xlsx Items!X1639 = 0.391 (table had 0.3) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 1 certain): D4@BORE_A 0.3 -&gt; OMi 0.391 (Items!X1639, M158)</t>
+        </is>
+      </c>
       <c r="AD20" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2846,7 +2912,7 @@
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
@@ -2854,7 +2920,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC21" s="3" t="inlineStr"/>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.5~1.50; HEXB@HEX=1~1.000; D3@BORE_B=0.3~0.297; D4@BORE_A=0.48~0.484</t>
+        </is>
+      </c>
       <c r="AD21" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2963,7 +3033,7 @@
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
@@ -2971,7 +3041,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC22" s="3" t="inlineStr"/>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.66~1.66; HEXB@HEX=1.25~1.250; D3@BORE_B=0.3~0.297; D4@BORE_A=0.61~0.609</t>
+        </is>
+      </c>
       <c r="AD22" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2990,7 +3064,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>1.3125</v>
@@ -3085,12 +3159,12 @@
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED)</t>
+          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); D1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1642 = 1.69 (table had 1.68) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A19 (user 2026-10-18, group 1 certain): D1@DRIVE 1.68 -&gt; OMi 1.69 (Items!L1642, M155)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3153,7 +3227,7 @@
         <v>37</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>0.39</v>
@@ -3206,10 +3280,14 @@
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
-        </is>
-      </c>
-      <c r="AC24" s="3" t="inlineStr"/>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1643 = 0.875 (table had 0.8125) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.8125 -&gt; OMi 0.875 (Items!R1643, M156)</t>
+        </is>
+      </c>
       <c r="AD24" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -3434,7 +3512,7 @@
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
@@ -3442,7 +3520,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC26" s="3" t="inlineStr"/>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.44~1.44; HEXB@HEX=0.8125~0.812; D3@BORE_B=0.39~0.391; D4@BORE_A=0.3~0.297</t>
+        </is>
+      </c>
       <c r="AD26" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -3668,7 +3750,7 @@
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
@@ -3676,7 +3758,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.6~1.60; HEXB@HEX=1~1.000; D3@BORE_B=0.39~0.391; D4@BORE_A=0.48~0.484</t>
+        </is>
+      </c>
       <c r="AD28" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -3785,7 +3871,7 @@
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
@@ -3793,7 +3879,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC29" s="3" t="inlineStr"/>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.76~1.76; HEXB@HEX=1.25~1.250; D3@BORE_B=0.39~0.391; D4@BORE_A=0.61~0.609</t>
+        </is>
+      </c>
       <c r="AD29" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -4016,7 +4106,7 @@
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
@@ -4026,7 +4116,7 @@
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.79~1.79; HEXB@HEX=1.5~1.500; D3@BORE_B=0.39~0.391; D4@BORE_A=0.84~0.844</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -4137,7 +4227,7 @@
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
@@ -4147,7 +4237,7 @@
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12)</t>
+          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.87~1.87; HEXB@HEX=1.875~1.875; D3@BORE_B=0.39~0.391; D4@BORE_A=1.08~1.078</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -4210,7 +4300,7 @@
         <v>37</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.9375</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>0.48</v>
@@ -4263,10 +4353,14 @@
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
-        </is>
-      </c>
-      <c r="AC33" s="3" t="inlineStr"/>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1651 = 1.000 (table had 0.9375) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.9375 -&gt; OMi 1.000 (Items!R1651, M156)</t>
+        </is>
+      </c>
       <c r="AD33" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -4327,7 +4421,7 @@
         <v>37</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.9375</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>0.48</v>
@@ -4380,10 +4474,14 @@
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
-        </is>
-      </c>
-      <c r="AC34" s="3" t="inlineStr"/>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1652 = 1.000 (table had 0.9375) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.9375 -&gt; OMi 1.000 (Items!R1652, M156)</t>
+        </is>
+      </c>
       <c r="AD34" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -4567,7 +4665,7 @@
         <v>0.48</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.48</v>
+        <v>0.609</v>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
@@ -4614,10 +4712,14 @@
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
-        </is>
-      </c>
-      <c r="AC36" s="3" t="inlineStr"/>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); D4@BORE_A: OMi WebsitePartsInfo2026.xlsx Items!X1654 = 0.609 (table had 0.48) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 1 certain): D4@BORE_A 0.48 -&gt; OMi 0.609 (Items!X1654, M158)</t>
+        </is>
+      </c>
       <c r="AD36" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -4726,7 +4828,7 @@
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
@@ -4736,7 +4838,7 @@
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.89~1.89; HEXB@HEX=1.5~1.500; D3@BORE_B=0.48~0.484; D4@BORE_A=0.84~0.844</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -4847,7 +4949,7 @@
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
@@ -4855,7 +4957,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC38" s="3" t="inlineStr"/>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.86~1.86; HEXB@HEX=1.125~1.125; D3@BORE_B=0.61~0.609; D4@BORE_A=0.3~0.297</t>
+        </is>
+      </c>
       <c r="AD38" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -4964,7 +5070,7 @@
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
@@ -4972,7 +5078,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC39" s="3" t="inlineStr"/>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.94~1.94; HEXB@HEX=1.125~1.125; D3@BORE_B=0.61~0.609; D4@BORE_A=0.39~0.391</t>
+        </is>
+      </c>
       <c r="AD39" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -5081,7 +5191,7 @@
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
@@ -5089,7 +5199,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC40" s="3" t="inlineStr"/>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.88~1.88; HEXB@HEX=1.125~1.125; D3@BORE_B=0.61~0.609; D4@BORE_A=0.48~0.484</t>
+        </is>
+      </c>
       <c r="AD40" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -5236,7 +5350,9 @@
       <c r="E42" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="F42" s="4" t="n"/>
+      <c r="F42" s="4" t="n">
+        <v>0.125</v>
+      </c>
       <c r="G42" s="4" t="n">
         <v>1.5877</v>
       </c>
@@ -5313,7 +5429,7 @@
       </c>
       <c r="AA42" s="4" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AB42" s="4" t="inlineStr">
@@ -5323,7 +5439,7 @@
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED - ORB groove width unpublished for this boss dash; row intentionally EXCLUDED from DesignTable_6400_SW2.xlsx so no SolidWorks configuration is generated. Part IS in OMi scope. Unblocks on one Brennan STEP measurement of an ORB -14 and an ORB -32; then restore the row.</t>
+          <t>BLOCKED - ORB groove width unpublished for this boss dash; row intentionally EXCLUDED from DesignTable_6400_SW2.xlsx so no SolidWorks configuration is generated. Part IS in OMi scope. Unblocks on one Brennan STEP measurement of an ORB -14 and an ORB -32; then restore the row. | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): ORB -14 groove width 0.125 from the end library (Brennan 6400-14 STEP of the same ORB size; Q-TRANSFER-ORBGW); every other cell already filled (Air-Way = OMi = Brennan catalog)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -5434,7 +5550,7 @@
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
@@ -5444,7 +5560,7 @@
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=1.99~1.99; HEXB@HEX=1.5~1.500; D3@BORE_B=0.61~0.609; D4@BORE_A=0.84~0.844</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -5555,7 +5671,7 @@
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
@@ -5565,7 +5681,7 @@
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12)</t>
+          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=2.08~2.08; HEXB@HEX=1.875~1.875; D3@BORE_B=0.61~0.609; D4@BORE_A=1.08~1.078</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -5676,7 +5792,7 @@
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
@@ -5686,7 +5802,7 @@
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=2.15~2.15; HEXB@HEX=2.125~2.125; D3@BORE_B=0.61~0.609; D4@BORE_A=1.31~1.312</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -5834,7 +5950,9 @@
       <c r="E47" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="F47" s="4" t="n"/>
+      <c r="F47" s="4" t="n">
+        <v>0.125</v>
+      </c>
       <c r="G47" s="4" t="n">
         <v>1.5877</v>
       </c>
@@ -5911,17 +6029,17 @@
       </c>
       <c r="AA47" s="4" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AB47" s="4" t="inlineStr">
         <is>
-          <t>INCOMPLETE</t>
+          <t>[BRENNAN-ONLY 2026-10-18] INCOMPLETE -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="AC47" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED - ORB groove width unpublished for this boss dash; row intentionally EXCLUDED from DesignTable_6400_SW2.xlsx so no SolidWorks configuration is generated. Part IS in OMi scope. Unblocks on one Brennan STEP measurement of an ORB -14 and an ORB -32; then restore the row.</t>
+          <t>BLOCKED - ORB groove width unpublished for this boss dash; row intentionally EXCLUDED from DesignTable_6400_SW2.xlsx so no SolidWorks configuration is generated. Part IS in OMi scope. Unblocks on one Brennan STEP measurement of an ORB -14 and an ORB -32; then restore the row. | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): ORB -14 groove width 0.125 from this part's own Brennan STEP; every other cell already filled (Air-Way = OMi = Brennan catalog)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -5932,6 +6050,11 @@
       <c r="AE47" t="inlineStr">
         <is>
           <t>6400-14-14-O</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6271,7 @@
       </c>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB49" s="3" t="inlineStr">
@@ -6156,7 +6279,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC49" s="3" t="inlineStr"/>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=2.01~2.01; HEXB@HEX=1.375~1.375; D3@BORE_B=0.84~0.844; D4@BORE_A=0.39~0.391</t>
+        </is>
+      </c>
       <c r="AD49" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -6265,7 +6392,7 @@
       </c>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
@@ -6273,7 +6400,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC50" s="3" t="inlineStr"/>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=2.07~2.07; HEXB@HEX=1.375~1.375; D3@BORE_B=0.84~0.844; D4@BORE_A=0.48~0.484</t>
+        </is>
+      </c>
       <c r="AD50" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -6382,7 +6513,7 @@
       </c>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
@@ -6390,7 +6521,11 @@
           <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED)</t>
         </is>
       </c>
-      <c r="AC51" s="3" t="inlineStr"/>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=2.04~2.04; HEXB@HEX=1.375~1.375; D3@BORE_B=0.84~0.844; D4@BORE_A=0.61~0.609</t>
+        </is>
+      </c>
       <c r="AD51" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -6420,7 +6555,9 @@
       <c r="E52" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="F52" s="4" t="n"/>
+      <c r="F52" s="4" t="n">
+        <v>0.125</v>
+      </c>
       <c r="G52" s="4" t="n">
         <v>1.5877</v>
       </c>
@@ -6497,7 +6634,7 @@
       </c>
       <c r="AA52" s="4" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AB52" s="4" t="inlineStr">
@@ -6507,7 +6644,7 @@
       </c>
       <c r="AC52" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED - ORB groove width unpublished for this boss dash; row intentionally EXCLUDED from DesignTable_6400_SW2.xlsx so no SolidWorks configuration is generated. Part IS in OMi scope. Unblocks on one Brennan STEP measurement of an ORB -14 and an ORB -32; then restore the row.</t>
+          <t>BLOCKED - ORB groove width unpublished for this boss dash; row intentionally EXCLUDED from DesignTable_6400_SW2.xlsx so no SolidWorks configuration is generated. Part IS in OMi scope. Unblocks on one Brennan STEP measurement of an ORB -14 and an ORB -32; then restore the row. | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): ORB -14 groove width 0.125 from the end library (Brennan 6400-14 STEP of the same ORB size; Q-TRANSFER-ORBGW); every other cell already filled (Air-Way = OMi = Brennan catalog)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -6739,7 +6876,7 @@
       </c>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
@@ -6749,7 +6886,7 @@
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12)</t>
+          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=2.12~2.12; HEXB@HEX=1.875~1.875; D3@BORE_B=0.84~0.844; D4@BORE_A=1.08~1.078</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -6860,7 +6997,7 @@
       </c>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
@@ -6870,7 +7007,7 @@
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=2.2~2.20; HEXB@HEX=2.125~2.125; D3@BORE_B=0.84~0.844; D4@BORE_A=1.31~1.312</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -6981,7 +7118,7 @@
       </c>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
@@ -6991,12 +7128,17 @@
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p014-t03: agrees on D1@DRIVE, HEXB@HEX, D3@BORE_B, D4@BORE_A</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>6400-20-12-O</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7239,7 @@
       </c>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
@@ -7107,12 +7249,17 @@
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p014-t03: agrees on D1@DRIVE, HEXB@HEX, D3@BORE_B, D4@BORE_A</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>6400-20-16-O</t>
         </is>
       </c>
     </row>
@@ -7223,12 +7370,17 @@
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12) | DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12) | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p014-t03: agrees on D1@DRIVE, HEXB@HEX, D3@BORE_B, D4@BORE_A</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>6400-20-20-O</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7481,7 @@
       </c>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
@@ -7339,7 +7491,7 @@
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=2.24~2.24; HEXB@HEX=2.125~2.125; D3@BORE_B=1.08~1.078; D4@BORE_A=1.31~1.312</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -7371,7 +7523,9 @@
       <c r="E60" s="4" t="n">
         <v>2.381</v>
       </c>
-      <c r="F60" s="4" t="n"/>
+      <c r="F60" s="4" t="n">
+        <v>0.125</v>
+      </c>
       <c r="G60" s="4" t="n">
         <v>3.1754</v>
       </c>
@@ -7448,7 +7602,7 @@
       </c>
       <c r="AA60" s="4" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AB60" s="4" t="inlineStr">
@@ -7458,7 +7612,7 @@
       </c>
       <c r="AC60" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED - ORB groove width unpublished for this boss dash; row intentionally EXCLUDED from DesignTable_6400_SW2.xlsx so no SolidWorks configuration is generated. Part IS in OMi scope. Unblocks on one Brennan STEP measurement of an ORB -14 and an ORB -32; then restore the row.</t>
+          <t>BLOCKED - ORB groove width unpublished for this boss dash; row intentionally EXCLUDED from DesignTable_6400_SW2.xlsx so no SolidWorks configuration is generated. Part IS in OMi scope. Unblocks on one Brennan STEP measurement of an ORB -14 and an ORB -32; then restore the row. | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): ORB -32 groove width 0.125 from the end library (Brennan 6400-32 STEP of the same ORB size; Q-TRANSFER-ORBGW); every other cell already filled (Air-Way = OMi = Brennan catalog)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
@@ -7521,7 +7675,7 @@
         <v>37</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>2</v>
+        <v>2.125</v>
       </c>
       <c r="Q61" s="3" t="n">
         <v>1.31</v>
@@ -7574,12 +7728,12 @@
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED)</t>
+          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1682 = 2.125 (table had 2) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A19 (user 2026-10-18, group 1 certain): HEXB@HEX 2 -&gt; OMi 2.125 (Items!R1682, M156)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -7642,7 +7796,7 @@
         <v>37</v>
       </c>
       <c r="P62" s="3" t="n">
-        <v>2</v>
+        <v>2.125</v>
       </c>
       <c r="Q62" s="3" t="n">
         <v>1.31</v>
@@ -7695,12 +7849,12 @@
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED)</t>
+          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1683 = 2.125 (table had 2) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12)</t>
+          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12) | A19 (user 2026-10-18, group 1 certain): HEXB@HEX 2 -&gt; OMi 2.125 (Items!R1683, M156)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
@@ -7853,7 +8007,9 @@
       <c r="E64" s="4" t="n">
         <v>2.381</v>
       </c>
-      <c r="F64" s="4" t="n"/>
+      <c r="F64" s="4" t="n">
+        <v>0.125</v>
+      </c>
       <c r="G64" s="4" t="n">
         <v>3.1754</v>
       </c>
@@ -7930,7 +8086,7 @@
       </c>
       <c r="AA64" s="4" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AB64" s="4" t="inlineStr">
@@ -7940,7 +8096,7 @@
       </c>
       <c r="AC64" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED - ORB groove width unpublished for this boss dash; row intentionally EXCLUDED from DesignTable_6400_SW2.xlsx so no SolidWorks configuration is generated. Part IS in OMi scope. Unblocks on one Brennan STEP measurement of an ORB -14 and an ORB -32; then restore the row.</t>
+          <t>BLOCKED - ORB groove width unpublished for this boss dash; row intentionally EXCLUDED from DesignTable_6400_SW2.xlsx so no SolidWorks configuration is generated. Part IS in OMi scope. Unblocks on one Brennan STEP measurement of an ORB -14 and an ORB -32; then restore the row. | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): ORB -32 groove width 0.125 from the end library (Brennan 6400-32 STEP of the same ORB size; Q-TRANSFER-ORBGW); every other cell already filled (Air-Way = OMi = Brennan catalog)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
@@ -8051,7 +8207,7 @@
       </c>
       <c r="AA65" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB65" s="3" t="inlineStr">
@@ -8061,7 +8217,7 @@
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12)</t>
+          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=2.94~2.94; HEXB@HEX=2.625~2.625; D3@BORE_B=1.78~1.781; D4@BORE_A=1.08~1.078</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -8172,7 +8328,7 @@
       </c>
       <c r="AA66" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB66" s="3" t="inlineStr">
@@ -8182,7 +8338,7 @@
       </c>
       <c r="AC66" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on D1@DRIVE=2.94~2.94; HEXB@HEX=2.625~2.625; D3@BORE_B=1.78~1.781; D4@BORE_A=1.31~1.312</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
@@ -8214,7 +8370,9 @@
       <c r="E67" s="4" t="n">
         <v>2.381</v>
       </c>
-      <c r="F67" s="4" t="n"/>
+      <c r="F67" s="4" t="n">
+        <v>0.125</v>
+      </c>
       <c r="G67" s="4" t="n">
         <v>3.1754</v>
       </c>
@@ -8291,17 +8449,17 @@
       </c>
       <c r="AA67" s="4" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AB67" s="4" t="inlineStr">
         <is>
-          <t>INCOMPLETE</t>
+          <t>[BRENNAN-ONLY 2026-10-18] INCOMPLETE -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="AC67" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED - ORB groove width unpublished for this boss dash; row intentionally EXCLUDED from DesignTable_6400_SW2.xlsx so no SolidWorks configuration is generated. Part IS in OMi scope. Unblocks on one Brennan STEP measurement of an ORB -14 and an ORB -32; then restore the row.</t>
+          <t>BLOCKED - ORB groove width unpublished for this boss dash; row intentionally EXCLUDED from DesignTable_6400_SW2.xlsx so no SolidWorks configuration is generated. Part IS in OMi scope. Unblocks on one Brennan STEP measurement of an ORB -14 and an ORB -32; then restore the row. | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): ORB -32 groove width 0.125 from this part's own Brennan STEP; every other cell already filled (Air-Way = OMi = Brennan catalog)</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -8312,6 +8470,11 @@
       <c r="AE67" t="inlineStr">
         <is>
           <t>6400-32-32-O</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6400.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6400.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Lookups" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookups" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2749,7 +2749,7 @@
         <v>0.3</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.391</v>
+        <v>0.3</v>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
@@ -2796,12 +2796,12 @@
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); D4@BORE_A: OMi WebsitePartsInfo2026.xlsx Items!X1639 = 0.391 (table had 0.3) [user 2026-10-18 A19]</t>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); D4@BORE_A: OMi WebsitePartsInfo2026.xlsx Items!X1639 = 0.391 (table had 0.3) [user 2026-10-18 A19]; D4@BORE_A: Air-Way 0.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 1 certain): D4@BORE_A 0.3 -&gt; OMi 0.391 (Items!X1639, M158)</t>
+          <t>A19 (user 2026-10-18, group 1 certain): D4@BORE_A 0.3 -&gt; OMi 0.391 (Items!X1639, M158) | 2026-10-20 Air-Way first: D4@BORE_A OMi/Brennan 0.391 -&gt; Air-Way 0.3</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>1.3125</v>
@@ -3159,12 +3159,12 @@
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); D1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1642 = 1.69 (table had 1.68) [user 2026-10-18 A19]</t>
+          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); D1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1642 = 1.69 (table had 1.68) [user 2026-10-18 A19]; D1@DRIVE: Air-Way 1.68 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.69) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A19 (user 2026-10-18, group 1 certain): D1@DRIVE 1.68 -&gt; OMi 1.69 (Items!L1642, M155)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A19 (user 2026-10-18, group 1 certain): D1@DRIVE 1.68 -&gt; OMi 1.69 (Items!L1642, M155) | 2026-10-20 Air-Way first: D1@DRIVE OMi/Brennan 1.69 -&gt; Air-Way 1.68</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3227,7 +3227,7 @@
         <v>37</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.875</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>0.39</v>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1643 = 0.875 (table had 0.8125) [user 2026-10-18 A19]</t>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1643 = 0.875 (table had 0.8125) [user 2026-10-18 A19]; HEXB@HEX: Air-Way 0.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.8125 -&gt; OMi 0.875 (Items!R1643, M156)</t>
+          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.8125 -&gt; OMi 0.875 (Items!R1643, M156) | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 0.875 -&gt; Air-Way 0.81</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4300,7 +4300,7 @@
         <v>37</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>0.48</v>
@@ -4353,12 +4353,12 @@
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1651 = 1.000 (table had 0.9375) [user 2026-10-18 A19]</t>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1651 = 1.000 (table had 0.9375) [user 2026-10-18 A19]; HEXB@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.9375 -&gt; OMi 1.000 (Items!R1651, M156)</t>
+          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.9375 -&gt; OMi 1.000 (Items!R1651, M156) | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 1 -&gt; Air-Way 0.94</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -4421,7 +4421,7 @@
         <v>37</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>0.48</v>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1652 = 1.000 (table had 0.9375) [user 2026-10-18 A19]</t>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1652 = 1.000 (table had 0.9375) [user 2026-10-18 A19]; HEXB@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.9375 -&gt; OMi 1.000 (Items!R1652, M156)</t>
+          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.9375 -&gt; OMi 1.000 (Items!R1652, M156) | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 1 -&gt; Air-Way 0.94</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -4665,7 +4665,7 @@
         <v>0.48</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.609</v>
+        <v>0.48</v>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); D4@BORE_A: OMi WebsitePartsInfo2026.xlsx Items!X1654 = 0.609 (table had 0.48) [user 2026-10-18 A19]</t>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); D4@BORE_A: OMi WebsitePartsInfo2026.xlsx Items!X1654 = 0.609 (table had 0.48) [user 2026-10-18 A19]; D4@BORE_A: Air-Way 0.48 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.609) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 1 certain): D4@BORE_A 0.48 -&gt; OMi 0.609 (Items!X1654, M158)</t>
+          <t>A19 (user 2026-10-18, group 1 certain): D4@BORE_A 0.48 -&gt; OMi 0.609 (Items!X1654, M158) | 2026-10-20 Air-Way first: D4@BORE_A OMi/Brennan 0.609 -&gt; Air-Way 0.48</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -7675,7 +7675,7 @@
         <v>37</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>2.125</v>
+        <v>2</v>
       </c>
       <c r="Q61" s="3" t="n">
         <v>1.31</v>
@@ -7728,12 +7728,12 @@
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1682 = 2.125 (table had 2) [user 2026-10-18 A19]</t>
+          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1682 = 2.125 (table had 2) [user 2026-10-18 A19]; HEXB@HEX: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.125) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A19 (user 2026-10-18, group 1 certain): HEXB@HEX 2 -&gt; OMi 2.125 (Items!R1682, M156)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A19 (user 2026-10-18, group 1 certain): HEXB@HEX 2 -&gt; OMi 2.125 (Items!R1682, M156) | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 2.125 -&gt; Air-Way 2</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -7796,7 +7796,7 @@
         <v>37</v>
       </c>
       <c r="P62" s="3" t="n">
-        <v>2.125</v>
+        <v>2</v>
       </c>
       <c r="Q62" s="3" t="n">
         <v>1.31</v>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1683 = 2.125 (table had 2) [user 2026-10-18 A19]</t>
+          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1683 = 2.125 (table had 2) [user 2026-10-18 A19]; HEXB@HEX: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.125) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12) | A19 (user 2026-10-18, group 1 certain): HEXB@HEX 2 -&gt; OMi 2.125 (Items!R1683, M156)</t>
+          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12) | A19 (user 2026-10-18, group 1 certain): HEXB@HEX 2 -&gt; OMi 2.125 (Items!R1683, M156) | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 2.125 -&gt; Air-Way 2</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
